--- a/major_data_all.xlsx
+++ b/major_data_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\教育company\办公司\doubaozhiyuan-final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laoya\Desktop\nihao\doubaozhiyuan-final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA61E090-7443-41F2-998F-2E835C38AE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E14527E-5017-447E-A65B-F647F1AA4FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>一级学科ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,11 +75,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>满意度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>开设院校数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专业转行率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深造率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,13 +432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="14" width="10.58203125" customWidth="1"/>
+    <col min="1" max="14" width="10.58203125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,315 +477,14 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
